--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6188,6 +6188,961 @@
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120488571</v>
+      </c>
+      <c r="B50" t="n">
+        <v>86367</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>449</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cortinarius fraudulosus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>706339</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6634899</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>120488592</v>
+      </c>
+      <c r="B51" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>706338</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6634985</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>120488582</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91879</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus s.str.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>706338</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6634958</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>120488594</v>
+      </c>
+      <c r="B53" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>706329</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6634924</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>120488569</v>
+      </c>
+      <c r="B54" t="n">
+        <v>86470</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>706333</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6634901</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120488558</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91879</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus s.str.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>706333</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6634901</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>120488575</v>
+      </c>
+      <c r="B56" t="n">
+        <v>86470</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>706308</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6634928</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>120488593</v>
+      </c>
+      <c r="B57" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>706324</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6634966</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>120488595</v>
+      </c>
+      <c r="B58" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>706297</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6634904</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -6190,10 +6190,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120488571</v>
+        <v>120488582</v>
       </c>
       <c r="B50" t="n">
-        <v>86367</v>
+        <v>91879</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6202,25 +6202,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>449</v>
+        <v>5964</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>706339</v>
+        <v>706338</v>
       </c>
       <c r="R50" t="n">
-        <v>6634899</v>
+        <v>6634958</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6274,7 +6274,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6297,7 +6296,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120488592</v>
+        <v>120488595</v>
       </c>
       <c r="B51" t="n">
         <v>100194</v>
@@ -6337,10 +6336,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706338</v>
+        <v>706297</v>
       </c>
       <c r="R51" t="n">
-        <v>6634985</v>
+        <v>6634904</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6403,10 +6402,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120488582</v>
+        <v>120488593</v>
       </c>
       <c r="B52" t="n">
-        <v>91879</v>
+        <v>100194</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6419,21 +6418,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6443,10 +6442,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706338</v>
+        <v>706324</v>
       </c>
       <c r="R52" t="n">
-        <v>6634958</v>
+        <v>6634966</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6509,7 +6508,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120488594</v>
+        <v>120488592</v>
       </c>
       <c r="B53" t="n">
         <v>100194</v>
@@ -6549,10 +6548,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>706329</v>
+        <v>706338</v>
       </c>
       <c r="R53" t="n">
-        <v>6634924</v>
+        <v>6634985</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6615,10 +6614,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120488569</v>
+        <v>120488571</v>
       </c>
       <c r="B54" t="n">
-        <v>86470</v>
+        <v>86367</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6627,25 +6626,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3739</v>
+        <v>449</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6655,10 +6654,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>706333</v>
+        <v>706339</v>
       </c>
       <c r="R54" t="n">
-        <v>6634901</v>
+        <v>6634899</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6699,6 +6698,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6721,10 +6721,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120488558</v>
+        <v>120488569</v>
       </c>
       <c r="B55" t="n">
-        <v>91879</v>
+        <v>86470</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6733,25 +6733,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5964</v>
+        <v>3739</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6827,10 +6827,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120488575</v>
+        <v>120488594</v>
       </c>
       <c r="B56" t="n">
-        <v>86470</v>
+        <v>100194</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6839,25 +6839,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3739</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6867,10 +6867,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706308</v>
+        <v>706329</v>
       </c>
       <c r="R56" t="n">
-        <v>6634928</v>
+        <v>6634924</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6933,10 +6933,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120488593</v>
+        <v>120488575</v>
       </c>
       <c r="B57" t="n">
-        <v>100194</v>
+        <v>86470</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6945,25 +6945,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>3739</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6973,10 +6973,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706324</v>
+        <v>706308</v>
       </c>
       <c r="R57" t="n">
-        <v>6634966</v>
+        <v>6634928</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7039,10 +7039,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120488595</v>
+        <v>120488558</v>
       </c>
       <c r="B58" t="n">
-        <v>100194</v>
+        <v>91879</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7055,21 +7055,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7079,10 +7079,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>706297</v>
+        <v>706333</v>
       </c>
       <c r="R58" t="n">
-        <v>6634904</v>
+        <v>6634901</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7143,6 +7143,112 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120520067</v>
+      </c>
+      <c r="B59" t="n">
+        <v>91200</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>706226</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6634894</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -6190,10 +6190,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120488582</v>
+        <v>120488592</v>
       </c>
       <c r="B50" t="n">
-        <v>91879</v>
+        <v>100194</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6206,21 +6206,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6233,7 +6233,7 @@
         <v>706338</v>
       </c>
       <c r="R50" t="n">
-        <v>6634958</v>
+        <v>6634985</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6296,10 +6296,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120488595</v>
+        <v>120488571</v>
       </c>
       <c r="B51" t="n">
-        <v>100194</v>
+        <v>86367</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6308,25 +6308,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>449</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706297</v>
+        <v>706339</v>
       </c>
       <c r="R51" t="n">
-        <v>6634904</v>
+        <v>6634899</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6380,6 +6380,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6402,10 +6403,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120488593</v>
+        <v>120488569</v>
       </c>
       <c r="B52" t="n">
-        <v>100194</v>
+        <v>86470</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6414,25 +6415,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>3739</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6442,10 +6443,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706324</v>
+        <v>706333</v>
       </c>
       <c r="R52" t="n">
-        <v>6634966</v>
+        <v>6634901</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6508,10 +6509,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120488592</v>
+        <v>120488558</v>
       </c>
       <c r="B53" t="n">
-        <v>100194</v>
+        <v>91879</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6524,21 +6525,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6548,10 +6549,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>706338</v>
+        <v>706333</v>
       </c>
       <c r="R53" t="n">
-        <v>6634985</v>
+        <v>6634901</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6614,10 +6615,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120488571</v>
+        <v>120488593</v>
       </c>
       <c r="B54" t="n">
-        <v>86367</v>
+        <v>100194</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6626,25 +6627,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>449</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6654,10 +6655,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>706339</v>
+        <v>706324</v>
       </c>
       <c r="R54" t="n">
-        <v>6634899</v>
+        <v>6634966</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6698,7 +6699,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6721,7 +6721,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120488569</v>
+        <v>120488575</v>
       </c>
       <c r="B55" t="n">
         <v>86470</v>
@@ -6761,10 +6761,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706333</v>
+        <v>706308</v>
       </c>
       <c r="R55" t="n">
-        <v>6634901</v>
+        <v>6634928</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6827,7 +6827,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120488594</v>
+        <v>120488595</v>
       </c>
       <c r="B56" t="n">
         <v>100194</v>
@@ -6867,10 +6867,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706329</v>
+        <v>706297</v>
       </c>
       <c r="R56" t="n">
-        <v>6634924</v>
+        <v>6634904</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6933,10 +6933,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120488575</v>
+        <v>120488594</v>
       </c>
       <c r="B57" t="n">
-        <v>86470</v>
+        <v>100194</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6945,25 +6945,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3739</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6973,10 +6973,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706308</v>
+        <v>706329</v>
       </c>
       <c r="R57" t="n">
-        <v>6634928</v>
+        <v>6634924</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7039,7 +7039,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120488558</v>
+        <v>120488582</v>
       </c>
       <c r="B58" t="n">
         <v>91879</v>
@@ -7079,10 +7079,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>706333</v>
+        <v>706338</v>
       </c>
       <c r="R58" t="n">
-        <v>6634901</v>
+        <v>6634958</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -6190,7 +6190,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120488592</v>
+        <v>120488593</v>
       </c>
       <c r="B50" t="n">
         <v>100194</v>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>706338</v>
+        <v>706324</v>
       </c>
       <c r="R50" t="n">
-        <v>6634985</v>
+        <v>6634966</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6296,10 +6296,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120488571</v>
+        <v>120488569</v>
       </c>
       <c r="B51" t="n">
-        <v>86367</v>
+        <v>86470</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6308,25 +6308,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>449</v>
+        <v>3739</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706339</v>
+        <v>706333</v>
       </c>
       <c r="R51" t="n">
-        <v>6634899</v>
+        <v>6634901</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6380,7 +6380,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6403,10 +6402,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120488569</v>
+        <v>120488594</v>
       </c>
       <c r="B52" t="n">
-        <v>86470</v>
+        <v>100194</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6415,25 +6414,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3739</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6443,10 +6442,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706333</v>
+        <v>706329</v>
       </c>
       <c r="R52" t="n">
-        <v>6634901</v>
+        <v>6634924</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6509,7 +6508,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120488558</v>
+        <v>120488582</v>
       </c>
       <c r="B53" t="n">
         <v>91879</v>
@@ -6549,10 +6548,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>706333</v>
+        <v>706338</v>
       </c>
       <c r="R53" t="n">
-        <v>6634901</v>
+        <v>6634958</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6615,10 +6614,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120488593</v>
+        <v>120488558</v>
       </c>
       <c r="B54" t="n">
-        <v>100194</v>
+        <v>91879</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6631,21 +6630,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6655,10 +6654,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>706324</v>
+        <v>706333</v>
       </c>
       <c r="R54" t="n">
-        <v>6634966</v>
+        <v>6634901</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6721,10 +6720,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120488575</v>
+        <v>120488595</v>
       </c>
       <c r="B55" t="n">
-        <v>86470</v>
+        <v>100194</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6733,25 +6732,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3739</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6761,10 +6760,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706308</v>
+        <v>706297</v>
       </c>
       <c r="R55" t="n">
-        <v>6634928</v>
+        <v>6634904</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6827,10 +6826,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120488595</v>
+        <v>120488575</v>
       </c>
       <c r="B56" t="n">
-        <v>100194</v>
+        <v>86470</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6839,25 +6838,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>3739</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6867,10 +6866,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706297</v>
+        <v>706308</v>
       </c>
       <c r="R56" t="n">
-        <v>6634904</v>
+        <v>6634928</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6933,10 +6932,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120488594</v>
+        <v>120488571</v>
       </c>
       <c r="B57" t="n">
-        <v>100194</v>
+        <v>86367</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6945,25 +6944,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>449</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6973,10 +6972,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706329</v>
+        <v>706339</v>
       </c>
       <c r="R57" t="n">
-        <v>6634924</v>
+        <v>6634899</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7017,6 +7016,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7039,10 +7039,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120488582</v>
+        <v>120488592</v>
       </c>
       <c r="B58" t="n">
-        <v>91879</v>
+        <v>100194</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7055,21 +7055,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7082,7 +7082,7 @@
         <v>706338</v>
       </c>
       <c r="R58" t="n">
-        <v>6634958</v>
+        <v>6634985</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -5275,7 +5275,7 @@
         <v>119129153</v>
       </c>
       <c r="B41" t="n">
-        <v>91180</v>
+        <v>91312</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5306,6 +5306,9 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Haggård, Upl</t>
@@ -5356,6 +5359,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5370,7 +5374,11 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5479,7 +5487,7 @@
         <v>119129161</v>
       </c>
       <c r="B43" t="n">
-        <v>91180</v>
+        <v>91312</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5510,6 +5518,9 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Haggård, Upl</t>
@@ -5560,6 +5571,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5574,7 +5586,11 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5785,7 +5801,7 @@
         <v>119129160</v>
       </c>
       <c r="B46" t="n">
-        <v>91180</v>
+        <v>91312</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5816,6 +5832,9 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Haggård, Upl</t>
@@ -5866,6 +5885,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5880,7 +5900,11 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5989,7 +6013,7 @@
         <v>119129159</v>
       </c>
       <c r="B48" t="n">
-        <v>91180</v>
+        <v>91312</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6020,6 +6044,9 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Haggård, Upl</t>
@@ -6070,6 +6097,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6084,7 +6112,11 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6511,7 +6543,7 @@
         <v>120488571</v>
       </c>
       <c r="B53" t="n">
-        <v>86171</v>
+        <v>86178</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6542,6 +6574,9 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Haggård, Upl</t>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -5275,7 +5275,7 @@
         <v>119129153</v>
       </c>
       <c r="B41" t="n">
-        <v>91312</v>
+        <v>91324</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>119129161</v>
       </c>
       <c r="B43" t="n">
-        <v>91312</v>
+        <v>91324</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>119129160</v>
       </c>
       <c r="B46" t="n">
-        <v>91312</v>
+        <v>91324</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>119129159</v>
       </c>
       <c r="B48" t="n">
-        <v>91312</v>
+        <v>91324</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>120488571</v>
       </c>
       <c r="B53" t="n">
-        <v>86178</v>
+        <v>86184</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -5275,7 +5275,7 @@
         <v>119129153</v>
       </c>
       <c r="B41" t="n">
-        <v>91324</v>
+        <v>91325</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>119129161</v>
       </c>
       <c r="B43" t="n">
-        <v>91324</v>
+        <v>91325</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>119129160</v>
       </c>
       <c r="B46" t="n">
-        <v>91324</v>
+        <v>91325</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>119129159</v>
       </c>
       <c r="B48" t="n">
-        <v>91324</v>
+        <v>91325</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -5275,7 +5275,7 @@
         <v>119129153</v>
       </c>
       <c r="B41" t="n">
-        <v>91325</v>
+        <v>91328</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>119129161</v>
       </c>
       <c r="B43" t="n">
-        <v>91325</v>
+        <v>91328</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>119129160</v>
       </c>
       <c r="B46" t="n">
-        <v>91325</v>
+        <v>91328</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>119129159</v>
       </c>
       <c r="B48" t="n">
-        <v>91325</v>
+        <v>91328</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>120488571</v>
       </c>
       <c r="B53" t="n">
-        <v>86184</v>
+        <v>86187</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -5275,7 +5275,7 @@
         <v>119129153</v>
       </c>
       <c r="B41" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>119129161</v>
       </c>
       <c r="B43" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>119129160</v>
       </c>
       <c r="B46" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>119129159</v>
       </c>
       <c r="B48" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>120488571</v>
       </c>
       <c r="B53" t="n">
-        <v>86187</v>
+        <v>86191</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -5275,7 +5275,7 @@
         <v>119129153</v>
       </c>
       <c r="B41" t="n">
-        <v>91334</v>
+        <v>91335</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>119129161</v>
       </c>
       <c r="B43" t="n">
-        <v>91334</v>
+        <v>91335</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>119129160</v>
       </c>
       <c r="B46" t="n">
-        <v>91334</v>
+        <v>91335</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>119129159</v>
       </c>
       <c r="B48" t="n">
-        <v>91334</v>
+        <v>91335</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>120488571</v>
       </c>
       <c r="B53" t="n">
-        <v>86191</v>
+        <v>86192</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -5275,7 +5275,7 @@
         <v>119129153</v>
       </c>
       <c r="B41" t="n">
-        <v>91335</v>
+        <v>91343</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>119129161</v>
       </c>
       <c r="B43" t="n">
-        <v>91335</v>
+        <v>91343</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
         <v>119129160</v>
       </c>
       <c r="B46" t="n">
-        <v>91335</v>
+        <v>91343</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>119129159</v>
       </c>
       <c r="B48" t="n">
-        <v>91335</v>
+        <v>91343</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>120488571</v>
       </c>
       <c r="B53" t="n">
-        <v>86192</v>
+        <v>86199</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -1400,7 +1400,7 @@
         <v>119058669</v>
       </c>
       <c r="B8" t="n">
-        <v>100288</v>
+        <v>100306</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>119058666</v>
       </c>
       <c r="B21" t="n">
-        <v>100288</v>
+        <v>100306</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>119058680</v>
       </c>
       <c r="B22" t="n">
-        <v>100379</v>
+        <v>100397</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -1400,7 +1400,7 @@
         <v>119058669</v>
       </c>
       <c r="B8" t="n">
-        <v>100306</v>
+        <v>100308</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>119058666</v>
       </c>
       <c r="B21" t="n">
-        <v>100306</v>
+        <v>100308</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>119058680</v>
       </c>
       <c r="B22" t="n">
-        <v>100397</v>
+        <v>100399</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -1400,7 +1400,7 @@
         <v>119058669</v>
       </c>
       <c r="B8" t="n">
-        <v>100308</v>
+        <v>100315</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>119058666</v>
       </c>
       <c r="B21" t="n">
-        <v>100308</v>
+        <v>100315</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>119058680</v>
       </c>
       <c r="B22" t="n">
-        <v>100399</v>
+        <v>100406</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -1400,7 +1400,7 @@
         <v>119058669</v>
       </c>
       <c r="B8" t="n">
-        <v>100315</v>
+        <v>100324</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>119058666</v>
       </c>
       <c r="B21" t="n">
-        <v>100315</v>
+        <v>100324</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>119058680</v>
       </c>
       <c r="B22" t="n">
-        <v>100406</v>
+        <v>100415</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -1400,7 +1400,7 @@
         <v>119058669</v>
       </c>
       <c r="B8" t="n">
-        <v>100324</v>
+        <v>100332</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>119058666</v>
       </c>
       <c r="B21" t="n">
-        <v>100324</v>
+        <v>100332</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>119058680</v>
       </c>
       <c r="B22" t="n">
-        <v>100415</v>
+        <v>100423</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7284,6 +7284,127 @@
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>122452996</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79595</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6441</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Slanklav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Collema flaccidum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>706191</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6634916</v>
+      </c>
+      <c r="S60" t="n">
+        <v>50</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7289,7 +7289,7 @@
         <v>122452996</v>
       </c>
       <c r="B60" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7289,7 +7289,7 @@
         <v>122452996</v>
       </c>
       <c r="B60" t="n">
-        <v>79600</v>
+        <v>79601</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7303,11 +7303,6 @@
       </c>
       <c r="E60" t="n">
         <v>6441</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Slanklav</t>
-        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7376,11 +7371,6 @@
       <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7289,7 +7289,7 @@
         <v>122452996</v>
       </c>
       <c r="B60" t="n">
-        <v>79601</v>
+        <v>79605</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7303,6 +7303,11 @@
       </c>
       <c r="E60" t="n">
         <v>6441</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Slanklav</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7371,6 +7376,11 @@
       <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7289,7 +7289,7 @@
         <v>122452996</v>
       </c>
       <c r="B60" t="n">
-        <v>79605</v>
+        <v>79606</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7289,7 +7289,7 @@
         <v>122452996</v>
       </c>
       <c r="B60" t="n">
-        <v>79606</v>
+        <v>79609</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7289,7 +7289,7 @@
         <v>122452996</v>
       </c>
       <c r="B60" t="n">
-        <v>79711</v>
+        <v>79715</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7405,6 +7405,434 @@
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>123823554</v>
+      </c>
+      <c r="B61" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Rantet, Rantet, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>706326</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6634890</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>123824338</v>
+      </c>
+      <c r="B62" t="n">
+        <v>91707</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1105</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Laxporing</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Rhodonia placenta</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Rantet, Rantet, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>706269</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6634937</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>123823682</v>
+      </c>
+      <c r="B63" t="n">
+        <v>94917</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Rantet, Rantet, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>706317</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6634941</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>123823666</v>
+      </c>
+      <c r="B64" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Rantet, Rantet, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>706292</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6634936</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7407,10 +7407,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123823554</v>
+        <v>123824338</v>
       </c>
       <c r="B61" t="n">
-        <v>100662</v>
+        <v>91712</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7419,25 +7419,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>1105</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706326</v>
+        <v>706269</v>
       </c>
       <c r="R61" t="n">
-        <v>6634890</v>
+        <v>6634937</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7493,6 +7493,26 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7509,10 +7529,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123824338</v>
+        <v>123823554</v>
       </c>
       <c r="B62" t="n">
-        <v>91707</v>
+        <v>100680</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7521,25 +7541,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1105</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7549,10 +7569,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706269</v>
+        <v>706326</v>
       </c>
       <c r="R62" t="n">
-        <v>6634937</v>
+        <v>6634890</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7595,26 +7615,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7631,10 +7631,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123823682</v>
+        <v>123823666</v>
       </c>
       <c r="B63" t="n">
-        <v>94917</v>
+        <v>100680</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7647,21 +7647,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7671,10 +7671,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706317</v>
+        <v>706292</v>
       </c>
       <c r="R63" t="n">
-        <v>6634941</v>
+        <v>6634936</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7733,10 +7733,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123823666</v>
+        <v>123823682</v>
       </c>
       <c r="B64" t="n">
-        <v>100662</v>
+        <v>94923</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7749,21 +7749,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7773,10 +7773,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706292</v>
+        <v>706317</v>
       </c>
       <c r="R64" t="n">
-        <v>6634936</v>
+        <v>6634941</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7407,10 +7407,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123824338</v>
+        <v>123823682</v>
       </c>
       <c r="B61" t="n">
-        <v>91712</v>
+        <v>94925</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7419,25 +7419,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1105</v>
+        <v>2818</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706269</v>
+        <v>706317</v>
       </c>
       <c r="R61" t="n">
-        <v>6634937</v>
+        <v>6634941</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7493,26 +7493,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7529,10 +7509,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123823554</v>
+        <v>123823666</v>
       </c>
       <c r="B62" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7569,10 +7549,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706326</v>
+        <v>706292</v>
       </c>
       <c r="R62" t="n">
-        <v>6634890</v>
+        <v>6634936</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7631,10 +7611,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123823666</v>
+        <v>123823554</v>
       </c>
       <c r="B63" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7671,10 +7651,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706292</v>
+        <v>706326</v>
       </c>
       <c r="R63" t="n">
-        <v>6634936</v>
+        <v>6634890</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7733,10 +7713,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123823682</v>
+        <v>123824338</v>
       </c>
       <c r="B64" t="n">
-        <v>94923</v>
+        <v>91714</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7745,25 +7725,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2818</v>
+        <v>1105</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7773,10 +7753,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706317</v>
+        <v>706269</v>
       </c>
       <c r="R64" t="n">
-        <v>6634941</v>
+        <v>6634937</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7819,6 +7799,26 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7410,7 +7410,7 @@
         <v>123823682</v>
       </c>
       <c r="B61" t="n">
-        <v>94925</v>
+        <v>95433</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7509,10 +7509,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123823666</v>
+        <v>123824338</v>
       </c>
       <c r="B62" t="n">
-        <v>100682</v>
+        <v>91714</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7521,25 +7521,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>1105</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7549,10 +7549,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706292</v>
+        <v>706269</v>
       </c>
       <c r="R62" t="n">
-        <v>6634936</v>
+        <v>6634937</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7595,6 +7595,26 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7614,7 +7634,7 @@
         <v>123823554</v>
       </c>
       <c r="B63" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7713,10 +7733,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123824338</v>
+        <v>123823666</v>
       </c>
       <c r="B64" t="n">
-        <v>91714</v>
+        <v>100257</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7725,25 +7745,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1105</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7753,10 +7773,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706269</v>
+        <v>706292</v>
       </c>
       <c r="R64" t="n">
-        <v>6634937</v>
+        <v>6634936</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7799,26 +7819,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7407,10 +7407,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123823682</v>
+        <v>123823666</v>
       </c>
       <c r="B61" t="n">
-        <v>95433</v>
+        <v>100257</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7423,21 +7423,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706317</v>
+        <v>706292</v>
       </c>
       <c r="R61" t="n">
-        <v>6634941</v>
+        <v>6634936</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7509,10 +7509,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123824338</v>
+        <v>123823554</v>
       </c>
       <c r="B62" t="n">
-        <v>91714</v>
+        <v>100257</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7521,25 +7521,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1105</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7549,10 +7549,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706269</v>
+        <v>706326</v>
       </c>
       <c r="R62" t="n">
-        <v>6634937</v>
+        <v>6634890</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7595,26 +7595,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7631,10 +7611,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123823554</v>
+        <v>123824338</v>
       </c>
       <c r="B63" t="n">
-        <v>100257</v>
+        <v>91714</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7643,25 +7623,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>1105</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7671,10 +7651,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706326</v>
+        <v>706269</v>
       </c>
       <c r="R63" t="n">
-        <v>6634890</v>
+        <v>6634937</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7717,6 +7697,26 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7733,10 +7733,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123823666</v>
+        <v>123823682</v>
       </c>
       <c r="B64" t="n">
-        <v>100257</v>
+        <v>95433</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7749,21 +7749,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7773,10 +7773,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706292</v>
+        <v>706317</v>
       </c>
       <c r="R64" t="n">
-        <v>6634936</v>
+        <v>6634941</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7407,10 +7407,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123823666</v>
+        <v>123823682</v>
       </c>
       <c r="B61" t="n">
-        <v>100257</v>
+        <v>95433</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7423,21 +7423,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706292</v>
+        <v>706317</v>
       </c>
       <c r="R61" t="n">
-        <v>6634936</v>
+        <v>6634941</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7509,10 +7509,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123823554</v>
+        <v>123824338</v>
       </c>
       <c r="B62" t="n">
-        <v>100257</v>
+        <v>91714</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7521,25 +7521,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>1105</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7549,10 +7549,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706326</v>
+        <v>706269</v>
       </c>
       <c r="R62" t="n">
-        <v>6634890</v>
+        <v>6634937</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7595,6 +7595,26 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7611,10 +7631,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123824338</v>
+        <v>123823554</v>
       </c>
       <c r="B63" t="n">
-        <v>91714</v>
+        <v>100257</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7623,25 +7643,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1105</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7651,10 +7671,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706269</v>
+        <v>706326</v>
       </c>
       <c r="R63" t="n">
-        <v>6634937</v>
+        <v>6634890</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7697,26 +7717,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7733,10 +7733,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123823682</v>
+        <v>123823666</v>
       </c>
       <c r="B64" t="n">
-        <v>95433</v>
+        <v>100257</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7749,21 +7749,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7773,10 +7773,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706317</v>
+        <v>706292</v>
       </c>
       <c r="R64" t="n">
-        <v>6634941</v>
+        <v>6634936</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7407,10 +7407,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123823682</v>
+        <v>123823666</v>
       </c>
       <c r="B61" t="n">
-        <v>95433</v>
+        <v>100257</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7423,21 +7423,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706317</v>
+        <v>706292</v>
       </c>
       <c r="R61" t="n">
-        <v>6634941</v>
+        <v>6634936</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7631,10 +7631,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123823554</v>
+        <v>123823682</v>
       </c>
       <c r="B63" t="n">
-        <v>100257</v>
+        <v>95433</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7647,21 +7647,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7671,10 +7671,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706326</v>
+        <v>706317</v>
       </c>
       <c r="R63" t="n">
-        <v>6634890</v>
+        <v>6634941</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7733,7 +7733,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123823666</v>
+        <v>123823554</v>
       </c>
       <c r="B64" t="n">
         <v>100257</v>
@@ -7773,10 +7773,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706292</v>
+        <v>706326</v>
       </c>
       <c r="R64" t="n">
-        <v>6634936</v>
+        <v>6634890</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7509,10 +7509,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123824338</v>
+        <v>123823682</v>
       </c>
       <c r="B62" t="n">
-        <v>91714</v>
+        <v>95433</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7521,25 +7521,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1105</v>
+        <v>2818</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7549,10 +7549,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706269</v>
+        <v>706317</v>
       </c>
       <c r="R62" t="n">
-        <v>6634937</v>
+        <v>6634941</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7595,26 +7595,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7631,10 +7611,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123823682</v>
+        <v>123824338</v>
       </c>
       <c r="B63" t="n">
-        <v>95433</v>
+        <v>91714</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7643,25 +7623,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2818</v>
+        <v>1105</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7671,10 +7651,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706317</v>
+        <v>706269</v>
       </c>
       <c r="R63" t="n">
-        <v>6634941</v>
+        <v>6634937</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7717,6 +7697,26 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7407,10 +7407,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123823666</v>
+        <v>123823682</v>
       </c>
       <c r="B61" t="n">
-        <v>100279</v>
+        <v>95455</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7423,21 +7423,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706292</v>
+        <v>706317</v>
       </c>
       <c r="R61" t="n">
-        <v>6634936</v>
+        <v>6634941</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7733,10 +7733,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123823682</v>
+        <v>123823666</v>
       </c>
       <c r="B64" t="n">
-        <v>95455</v>
+        <v>100279</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7749,21 +7749,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7773,10 +7773,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706317</v>
+        <v>706292</v>
       </c>
       <c r="R64" t="n">
-        <v>6634941</v>
+        <v>6634936</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7407,10 +7407,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123823682</v>
+        <v>123824338</v>
       </c>
       <c r="B61" t="n">
-        <v>95455</v>
+        <v>91736</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7419,25 +7419,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2818</v>
+        <v>1105</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706317</v>
+        <v>706269</v>
       </c>
       <c r="R61" t="n">
-        <v>6634941</v>
+        <v>6634937</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7493,6 +7493,26 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7509,10 +7529,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123823554</v>
+        <v>123823682</v>
       </c>
       <c r="B62" t="n">
-        <v>100279</v>
+        <v>95455</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7525,21 +7545,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7549,10 +7569,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706326</v>
+        <v>706317</v>
       </c>
       <c r="R62" t="n">
-        <v>6634890</v>
+        <v>6634941</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7611,10 +7631,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123824338</v>
+        <v>123823666</v>
       </c>
       <c r="B63" t="n">
-        <v>91736</v>
+        <v>100279</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7623,25 +7643,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1105</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7651,10 +7671,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706269</v>
+        <v>706292</v>
       </c>
       <c r="R63" t="n">
-        <v>6634937</v>
+        <v>6634936</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7697,26 +7717,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7733,7 +7733,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123823666</v>
+        <v>123823554</v>
       </c>
       <c r="B64" t="n">
         <v>100279</v>
@@ -7773,10 +7773,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706292</v>
+        <v>706326</v>
       </c>
       <c r="R64" t="n">
-        <v>6634936</v>
+        <v>6634890</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7407,10 +7407,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123824338</v>
+        <v>123823554</v>
       </c>
       <c r="B61" t="n">
-        <v>91736</v>
+        <v>100279</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7419,25 +7419,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1105</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706269</v>
+        <v>706326</v>
       </c>
       <c r="R61" t="n">
-        <v>6634937</v>
+        <v>6634890</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7493,26 +7493,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7529,10 +7509,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123823682</v>
+        <v>123823666</v>
       </c>
       <c r="B62" t="n">
-        <v>95455</v>
+        <v>100279</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7545,21 +7525,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7569,10 +7549,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706317</v>
+        <v>706292</v>
       </c>
       <c r="R62" t="n">
-        <v>6634941</v>
+        <v>6634936</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7631,10 +7611,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123823666</v>
+        <v>123823682</v>
       </c>
       <c r="B63" t="n">
-        <v>100279</v>
+        <v>95455</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7647,21 +7627,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7671,10 +7651,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706292</v>
+        <v>706317</v>
       </c>
       <c r="R63" t="n">
-        <v>6634936</v>
+        <v>6634941</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7733,10 +7713,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123823554</v>
+        <v>123824338</v>
       </c>
       <c r="B64" t="n">
-        <v>100279</v>
+        <v>91736</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7745,25 +7725,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>1105</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7773,10 +7753,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706326</v>
+        <v>706269</v>
       </c>
       <c r="R64" t="n">
-        <v>6634890</v>
+        <v>6634937</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7819,6 +7799,26 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -2820,7 +2820,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19" t="b">
         <v>0</v>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7833,6 +7833,410 @@
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>131431288</v>
+      </c>
+      <c r="B65" t="n">
+        <v>91813</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>706202</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6634961</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Kristina Jiselmark</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Värdefull natur i Stockholms län</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>131431286</v>
+      </c>
+      <c r="B66" t="n">
+        <v>101127</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>706291</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6635045</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Kristina Jiselmark</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Värdefull natur i Stockholms län</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>131431291</v>
+      </c>
+      <c r="B67" t="n">
+        <v>91780</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>706170</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6634898</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Kristina Jiselmark</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Värdefull natur i Stockholms län</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>131431292</v>
+      </c>
+      <c r="B68" t="n">
+        <v>92471</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>706150</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6634894</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Värdefull natur i Stockholms län</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7838,7 +7838,7 @@
         <v>131431288</v>
       </c>
       <c r="B65" t="n">
-        <v>91818</v>
+        <v>91824</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>131431286</v>
       </c>
       <c r="B66" t="n">
-        <v>101133</v>
+        <v>101139</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>131431291</v>
       </c>
       <c r="B67" t="n">
-        <v>91785</v>
+        <v>91791</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>131431292</v>
       </c>
       <c r="B68" t="n">
-        <v>92476</v>
+        <v>92482</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7939,7 +7939,7 @@
         <v>131431286</v>
       </c>
       <c r="B66" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>131431292</v>
       </c>
       <c r="B68" t="n">
-        <v>92482</v>
+        <v>92483</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7838,7 +7838,7 @@
         <v>131431288</v>
       </c>
       <c r="B65" t="n">
-        <v>91824</v>
+        <v>91825</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>131431286</v>
       </c>
       <c r="B66" t="n">
-        <v>101140</v>
+        <v>101141</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>131431291</v>
       </c>
       <c r="B67" t="n">
-        <v>91791</v>
+        <v>91792</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>131431292</v>
       </c>
       <c r="B68" t="n">
-        <v>92483</v>
+        <v>92484</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7838,7 +7838,7 @@
         <v>131431288</v>
       </c>
       <c r="B65" t="n">
-        <v>91825</v>
+        <v>91828</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>131431286</v>
       </c>
       <c r="B66" t="n">
-        <v>101141</v>
+        <v>101144</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>131431291</v>
       </c>
       <c r="B67" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>131431292</v>
       </c>
       <c r="B68" t="n">
-        <v>92484</v>
+        <v>92487</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7939,7 +7939,7 @@
         <v>131431286</v>
       </c>
       <c r="B66" t="n">
-        <v>101144</v>
+        <v>101145</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7838,7 +7838,7 @@
         <v>131431288</v>
       </c>
       <c r="B65" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>131431286</v>
       </c>
       <c r="B66" t="n">
-        <v>101145</v>
+        <v>101151</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>131431291</v>
       </c>
       <c r="B67" t="n">
-        <v>91795</v>
+        <v>91801</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>131431292</v>
       </c>
       <c r="B68" t="n">
-        <v>92487</v>
+        <v>92493</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7838,7 +7838,7 @@
         <v>131431288</v>
       </c>
       <c r="B65" t="n">
-        <v>91834</v>
+        <v>91837</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>131431286</v>
       </c>
       <c r="B66" t="n">
-        <v>101151</v>
+        <v>101154</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>131431291</v>
       </c>
       <c r="B67" t="n">
-        <v>91801</v>
+        <v>91804</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>131431292</v>
       </c>
       <c r="B68" t="n">
-        <v>92493</v>
+        <v>92496</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 24218-2024 artfynd.xlsx
+++ b/artfynd/A 24218-2024 artfynd.xlsx
@@ -7838,7 +7838,7 @@
         <v>131431288</v>
       </c>
       <c r="B65" t="n">
-        <v>91837</v>
+        <v>91842</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>131431286</v>
       </c>
       <c r="B66" t="n">
-        <v>101154</v>
+        <v>101159</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>131431291</v>
       </c>
       <c r="B67" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>131431292</v>
       </c>
       <c r="B68" t="n">
-        <v>92496</v>
+        <v>92501</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
